--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>All frequency options for fruit and vegetable consumption questions DH1 and DH3 from ATHIS 2025. Includes the 'Weiß nicht' option (code 'unknown').</t>
+    <t>All frequency options for fruit and vegetable consumption questions DH1 and DH3 from ATHIS 2025, including the two universal ATHIS metadata answers.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -139,6 +139,12 @@
   </si>
   <si>
     <t>Weiß nicht</t>
+  </si>
+  <si>
+    <t>meta-not-stated</t>
+  </si>
+  <si>
+    <t>Keine Angabe</t>
   </si>
   <si>
     <t>System URI</t>
@@ -416,7 +422,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -481,18 +487,26 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-nutrition-consumption-frequency-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
